--- a/static/data/quizz.xlsx
+++ b/static/data/quizz.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DERS\Archive\web\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B1815E-5C7E-4B05-9237-214E16483039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A95E354-605F-460E-A29D-E93B99D325D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1071,7 +1071,9 @@
       <c r="W2" s="3">
         <v>100</v>
       </c>
-      <c r="X2" s="3"/>
+      <c r="X2" s="3">
+        <v>90</v>
+      </c>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
@@ -1176,7 +1178,9 @@
       <c r="W3" s="3">
         <v>100</v>
       </c>
-      <c r="X3" s="3"/>
+      <c r="X3" s="3">
+        <v>95</v>
+      </c>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
@@ -1281,7 +1285,9 @@
       <c r="W4" s="3">
         <v>100</v>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3">
+        <v>85</v>
+      </c>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
@@ -1386,7 +1392,9 @@
       <c r="W5" s="3">
         <v>71</v>
       </c>
-      <c r="X5" s="3"/>
+      <c r="X5" s="3">
+        <v>80</v>
+      </c>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
@@ -1491,7 +1499,9 @@
       <c r="W6" s="3">
         <v>94</v>
       </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3">
+        <v>95</v>
+      </c>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
@@ -1596,7 +1606,9 @@
       <c r="W7" s="3">
         <v>74</v>
       </c>
-      <c r="X7" s="3"/>
+      <c r="X7" s="3">
+        <v>95</v>
+      </c>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
@@ -1701,7 +1713,9 @@
       <c r="W8" s="3">
         <v>97</v>
       </c>
-      <c r="X8" s="3"/>
+      <c r="X8" s="3">
+        <v>90</v>
+      </c>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
@@ -1806,7 +1820,9 @@
       <c r="W9" s="3">
         <v>89</v>
       </c>
-      <c r="X9" s="3"/>
+      <c r="X9" s="3">
+        <v>80</v>
+      </c>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
@@ -1911,7 +1927,9 @@
       <c r="W10" s="3">
         <v>74</v>
       </c>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3">
+        <v>100</v>
+      </c>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
@@ -2016,7 +2034,9 @@
       <c r="W11" s="3">
         <v>100</v>
       </c>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3">
+        <v>95</v>
+      </c>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
@@ -2121,7 +2141,9 @@
       <c r="W12" s="3">
         <v>83</v>
       </c>
-      <c r="X12" s="3"/>
+      <c r="X12" s="3">
+        <v>85</v>
+      </c>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
@@ -2226,7 +2248,9 @@
       <c r="W13" s="3">
         <v>89</v>
       </c>
-      <c r="X13" s="3"/>
+      <c r="X13" s="3">
+        <v>80</v>
+      </c>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
@@ -2331,7 +2355,9 @@
       <c r="W14" s="3">
         <v>94</v>
       </c>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3">
+        <v>100</v>
+      </c>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
@@ -2436,7 +2462,9 @@
       <c r="W15" s="3">
         <v>89</v>
       </c>
-      <c r="X15" s="3"/>
+      <c r="X15" s="3">
+        <v>60</v>
+      </c>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
@@ -2541,7 +2569,9 @@
       <c r="W16" s="3">
         <v>100</v>
       </c>
-      <c r="X16" s="3"/>
+      <c r="X16" s="3">
+        <v>90</v>
+      </c>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
@@ -2646,7 +2676,9 @@
       <c r="W17" s="3">
         <v>57</v>
       </c>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3">
+        <v>0</v>
+      </c>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
@@ -2707,19 +2739,19 @@
         <v>95</v>
       </c>
       <c r="I18" s="3">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="J18" s="3">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="L18" s="3">
         <v>0</v>
       </c>
       <c r="M18" s="3">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N18" s="3">
         <v>0</v>
@@ -2751,7 +2783,9 @@
       <c r="W18" s="3">
         <v>0</v>
       </c>
-      <c r="X18" s="3"/>
+      <c r="X18" s="3">
+        <v>0</v>
+      </c>
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
@@ -2856,7 +2890,9 @@
       <c r="W19" s="3">
         <v>83</v>
       </c>
-      <c r="X19" s="3"/>
+      <c r="X19" s="3">
+        <v>90</v>
+      </c>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
@@ -2961,7 +2997,9 @@
       <c r="W20" s="3">
         <v>74</v>
       </c>
-      <c r="X20" s="3"/>
+      <c r="X20" s="3">
+        <v>75</v>
+      </c>
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
@@ -3066,7 +3104,9 @@
       <c r="W21" s="3">
         <v>66</v>
       </c>
-      <c r="X21" s="3"/>
+      <c r="X21" s="3">
+        <v>60</v>
+      </c>
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
@@ -3171,7 +3211,9 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3"/>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
@@ -3276,7 +3318,9 @@
       <c r="W23" s="3">
         <v>0</v>
       </c>
-      <c r="X23" s="3"/>
+      <c r="X23" s="3">
+        <v>0</v>
+      </c>
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>

--- a/static/data/quizz.xlsx
+++ b/static/data/quizz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DERS\Archive\web\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A95E354-605F-460E-A29D-E93B99D325D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7A5635-4D01-4126-A9DD-50AEBF42EA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6960" yWindow="2520" windowWidth="13725" windowHeight="11865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-2024" sheetId="2" r:id="rId1"/>
@@ -2677,7 +2677,7 @@
         <v>57</v>
       </c>
       <c r="X17" s="3">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>

--- a/static/data/quizz.xlsx
+++ b/static/data/quizz.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DERS\Archive\web\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7A5635-4D01-4126-A9DD-50AEBF42EA09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3E4467-C4C7-48C9-9D21-8095CBCCF26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6960" yWindow="2520" windowWidth="13725" windowHeight="11865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-2024" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2023-2024'!$A$1:$BD$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2023-2024'!$A$1:$BE$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="78">
   <si>
     <t>İnformasiaya və informasiya prosesləri 1</t>
   </si>
@@ -823,14 +823,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BI23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="56" width="6.7109375" customWidth="1"/>
+    <col min="2" max="57" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="378" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:61" ht="378" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>11</v>
       </c>
@@ -903,105 +903,108 @@
       <c r="X1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Y1" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AD1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AF1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AG1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AH1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AI1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="AJ1" s="7" t="s">
+      <c r="AK1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AL1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AL1" s="7" t="s">
+      <c r="AM1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AM1" s="7" t="s">
+      <c r="AN1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AN1" s="7" t="s">
+      <c r="AO1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AO1" s="7" t="s">
+      <c r="AP1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AP1" s="7" t="s">
+      <c r="AQ1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="AQ1" s="6" t="s">
+      <c r="AR1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AR1" s="6" t="s">
+      <c r="AS1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AS1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="AU1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="AU1" s="7" t="s">
+      <c r="AV1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="AV1" s="7" t="s">
+      <c r="AW1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="AW1" s="7" t="s">
+      <c r="AX1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="AX1" s="6" t="s">
+      <c r="AY1" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="AY1" s="6" t="s">
+      <c r="AZ1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AZ1" s="6" t="s">
+      <c r="BA1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="BA1" s="6" t="s">
+      <c r="BB1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="BC1" s="6" t="s">
+      <c r="BD1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BE1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="BH1" s="8"/>
+      <c r="BI1" s="8"/>
     </row>
-    <row r="2" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>58</v>
       </c>
@@ -1074,8 +1077,12 @@
       <c r="X2" s="3">
         <v>90</v>
       </c>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
+      <c r="Y2" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>0</v>
+      </c>
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
@@ -1087,7 +1094,7 @@
       <c r="AI2" s="3"/>
       <c r="AJ2" s="3"/>
       <c r="AK2" s="3"/>
-      <c r="AL2" s="2"/>
+      <c r="AL2" s="3"/>
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
       <c r="AO2" s="2"/>
@@ -1106,9 +1113,10 @@
       <c r="BB2" s="2"/>
       <c r="BC2" s="2"/>
       <c r="BD2" s="2"/>
-      <c r="BE2" s="1"/>
+      <c r="BE2" s="2"/>
+      <c r="BF2" s="1"/>
     </row>
-    <row r="3" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
@@ -1181,8 +1189,12 @@
       <c r="X3" s="3">
         <v>95</v>
       </c>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
+      <c r="Y3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>0</v>
+      </c>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
@@ -1194,7 +1206,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
-      <c r="AL3" s="2"/>
+      <c r="AL3" s="3"/>
       <c r="AM3" s="2"/>
       <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
@@ -1213,9 +1225,10 @@
       <c r="BB3" s="2"/>
       <c r="BC3" s="2"/>
       <c r="BD3" s="2"/>
-      <c r="BE3" s="1"/>
+      <c r="BE3" s="2"/>
+      <c r="BF3" s="1"/>
     </row>
-    <row r="4" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A4" s="5" t="s">
         <v>59</v>
       </c>
@@ -1288,8 +1301,12 @@
       <c r="X4" s="3">
         <v>85</v>
       </c>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
+      <c r="Y4" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>91</v>
+      </c>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
@@ -1301,7 +1318,7 @@
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
-      <c r="AL4" s="2"/>
+      <c r="AL4" s="3"/>
       <c r="AM4" s="2"/>
       <c r="AN4" s="2"/>
       <c r="AO4" s="2"/>
@@ -1320,9 +1337,10 @@
       <c r="BB4" s="2"/>
       <c r="BC4" s="2"/>
       <c r="BD4" s="2"/>
-      <c r="BE4" s="1"/>
+      <c r="BE4" s="2"/>
+      <c r="BF4" s="1"/>
     </row>
-    <row r="5" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A5" s="5" t="s">
         <v>63</v>
       </c>
@@ -1395,8 +1413,12 @@
       <c r="X5" s="3">
         <v>80</v>
       </c>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
+      <c r="Y5" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>69</v>
+      </c>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
@@ -1408,7 +1430,7 @@
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
-      <c r="AL5" s="2"/>
+      <c r="AL5" s="3"/>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2"/>
       <c r="AO5" s="2"/>
@@ -1427,9 +1449,10 @@
       <c r="BB5" s="2"/>
       <c r="BC5" s="2"/>
       <c r="BD5" s="2"/>
-      <c r="BE5" s="1"/>
+      <c r="BE5" s="2"/>
+      <c r="BF5" s="1"/>
     </row>
-    <row r="6" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>61</v>
       </c>
@@ -1502,8 +1525,12 @@
       <c r="X6" s="3">
         <v>95</v>
       </c>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
+      <c r="Y6" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>83</v>
+      </c>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
@@ -1515,7 +1542,7 @@
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
-      <c r="AL6" s="2"/>
+      <c r="AL6" s="3"/>
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
       <c r="AO6" s="2"/>
@@ -1534,9 +1561,10 @@
       <c r="BB6" s="2"/>
       <c r="BC6" s="2"/>
       <c r="BD6" s="2"/>
-      <c r="BE6" s="1"/>
+      <c r="BE6" s="2"/>
+      <c r="BF6" s="1"/>
     </row>
-    <row r="7" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>52</v>
       </c>
@@ -1609,8 +1637,12 @@
       <c r="X7" s="3">
         <v>95</v>
       </c>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
+      <c r="Y7" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>91</v>
+      </c>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
@@ -1622,7 +1654,7 @@
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
-      <c r="AL7" s="2"/>
+      <c r="AL7" s="3"/>
       <c r="AM7" s="2"/>
       <c r="AN7" s="2"/>
       <c r="AO7" s="2"/>
@@ -1641,9 +1673,10 @@
       <c r="BB7" s="2"/>
       <c r="BC7" s="2"/>
       <c r="BD7" s="2"/>
-      <c r="BE7" s="1"/>
+      <c r="BE7" s="2"/>
+      <c r="BF7" s="1"/>
     </row>
-    <row r="8" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>67</v>
       </c>
@@ -1716,8 +1749,12 @@
       <c r="X8" s="3">
         <v>90</v>
       </c>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
+      <c r="Y8" s="3">
+        <v>33</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>71</v>
+      </c>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
@@ -1729,7 +1766,7 @@
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
-      <c r="AL8" s="2"/>
+      <c r="AL8" s="3"/>
       <c r="AM8" s="2"/>
       <c r="AN8" s="2"/>
       <c r="AO8" s="2"/>
@@ -1748,9 +1785,10 @@
       <c r="BB8" s="2"/>
       <c r="BC8" s="2"/>
       <c r="BD8" s="2"/>
-      <c r="BE8" s="1"/>
+      <c r="BE8" s="2"/>
+      <c r="BF8" s="1"/>
     </row>
-    <row r="9" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>64</v>
       </c>
@@ -1823,8 +1861,12 @@
       <c r="X9" s="3">
         <v>80</v>
       </c>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
+      <c r="Y9" s="3">
+        <v>55</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>77</v>
+      </c>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
@@ -1836,7 +1878,7 @@
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
-      <c r="AL9" s="2"/>
+      <c r="AL9" s="3"/>
       <c r="AM9" s="2"/>
       <c r="AN9" s="2"/>
       <c r="AO9" s="2"/>
@@ -1855,9 +1897,10 @@
       <c r="BB9" s="2"/>
       <c r="BC9" s="2"/>
       <c r="BD9" s="2"/>
-      <c r="BE9" s="1"/>
+      <c r="BE9" s="2"/>
+      <c r="BF9" s="1"/>
     </row>
-    <row r="10" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
@@ -1930,8 +1973,12 @@
       <c r="X10" s="3">
         <v>100</v>
       </c>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
+      <c r="Y10" s="3">
+        <v>61</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>0</v>
+      </c>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
@@ -1943,7 +1990,7 @@
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
-      <c r="AL10" s="2"/>
+      <c r="AL10" s="3"/>
       <c r="AM10" s="2"/>
       <c r="AN10" s="2"/>
       <c r="AO10" s="2"/>
@@ -1962,9 +2009,10 @@
       <c r="BB10" s="2"/>
       <c r="BC10" s="2"/>
       <c r="BD10" s="2"/>
-      <c r="BE10" s="1"/>
+      <c r="BE10" s="2"/>
+      <c r="BF10" s="1"/>
     </row>
-    <row r="11" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A11" s="5" t="s">
         <v>60</v>
       </c>
@@ -2037,8 +2085,12 @@
       <c r="X11" s="3">
         <v>95</v>
       </c>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
+      <c r="Y11" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>80</v>
+      </c>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
@@ -2050,7 +2102,7 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
-      <c r="AL11" s="2"/>
+      <c r="AL11" s="3"/>
       <c r="AM11" s="2"/>
       <c r="AN11" s="2"/>
       <c r="AO11" s="2"/>
@@ -2069,9 +2121,10 @@
       <c r="BB11" s="2"/>
       <c r="BC11" s="2"/>
       <c r="BD11" s="2"/>
-      <c r="BE11" s="1"/>
+      <c r="BE11" s="2"/>
+      <c r="BF11" s="1"/>
     </row>
-    <row r="12" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>55</v>
       </c>
@@ -2144,8 +2197,12 @@
       <c r="X12" s="3">
         <v>85</v>
       </c>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
+      <c r="Y12" s="3">
+        <v>49</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>94</v>
+      </c>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
@@ -2157,7 +2214,7 @@
       <c r="AI12" s="3"/>
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
-      <c r="AL12" s="2"/>
+      <c r="AL12" s="3"/>
       <c r="AM12" s="2"/>
       <c r="AN12" s="2"/>
       <c r="AO12" s="2"/>
@@ -2176,9 +2233,10 @@
       <c r="BB12" s="2"/>
       <c r="BC12" s="2"/>
       <c r="BD12" s="2"/>
-      <c r="BE12" s="1"/>
+      <c r="BE12" s="2"/>
+      <c r="BF12" s="1"/>
     </row>
-    <row r="13" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A13" s="5" t="s">
         <v>56</v>
       </c>
@@ -2251,8 +2309,12 @@
       <c r="X13" s="3">
         <v>80</v>
       </c>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>89</v>
+      </c>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
@@ -2264,7 +2326,7 @@
       <c r="AI13" s="3"/>
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
-      <c r="AL13" s="2"/>
+      <c r="AL13" s="3"/>
       <c r="AM13" s="2"/>
       <c r="AN13" s="2"/>
       <c r="AO13" s="2"/>
@@ -2283,9 +2345,10 @@
       <c r="BB13" s="2"/>
       <c r="BC13" s="2"/>
       <c r="BD13" s="2"/>
-      <c r="BE13" s="1"/>
+      <c r="BE13" s="2"/>
+      <c r="BF13" s="1"/>
     </row>
-    <row r="14" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
         <v>65</v>
       </c>
@@ -2358,8 +2421,12 @@
       <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
+      <c r="Y14" s="3">
+        <v>46</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>97</v>
+      </c>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
@@ -2371,14 +2438,14 @@
       <c r="AI14" s="3"/>
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
-      <c r="AL14" s="2"/>
+      <c r="AL14" s="3"/>
       <c r="AM14" s="2"/>
       <c r="AN14" s="2"/>
       <c r="AO14" s="2"/>
       <c r="AP14" s="2"/>
       <c r="AQ14" s="2"/>
-      <c r="AR14" s="10"/>
-      <c r="AS14" s="2"/>
+      <c r="AR14" s="2"/>
+      <c r="AS14" s="10"/>
       <c r="AT14" s="2"/>
       <c r="AU14" s="2"/>
       <c r="AV14" s="2"/>
@@ -2390,9 +2457,10 @@
       <c r="BB14" s="2"/>
       <c r="BC14" s="2"/>
       <c r="BD14" s="2"/>
-      <c r="BE14" s="1"/>
+      <c r="BE14" s="2"/>
+      <c r="BF14" s="1"/>
     </row>
-    <row r="15" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
         <v>57</v>
       </c>
@@ -2465,8 +2533,12 @@
       <c r="X15" s="3">
         <v>60</v>
       </c>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
+      <c r="Y15" s="3">
+        <v>55</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>46</v>
+      </c>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
@@ -2478,7 +2550,7 @@
       <c r="AI15" s="3"/>
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
-      <c r="AL15" s="2"/>
+      <c r="AL15" s="3"/>
       <c r="AM15" s="2"/>
       <c r="AN15" s="2"/>
       <c r="AO15" s="2"/>
@@ -2497,9 +2569,10 @@
       <c r="BB15" s="2"/>
       <c r="BC15" s="2"/>
       <c r="BD15" s="2"/>
-      <c r="BE15" s="1"/>
+      <c r="BE15" s="2"/>
+      <c r="BF15" s="1"/>
     </row>
-    <row r="16" spans="1:60" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:61" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
         <v>62</v>
       </c>
@@ -2572,8 +2645,12 @@
       <c r="X16" s="3">
         <v>90</v>
       </c>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
+      <c r="Y16" s="3">
+        <v>55</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>0</v>
+      </c>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
@@ -2585,7 +2662,7 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
-      <c r="AL16" s="2"/>
+      <c r="AL16" s="3"/>
       <c r="AM16" s="2"/>
       <c r="AN16" s="2"/>
       <c r="AO16" s="2"/>
@@ -2604,9 +2681,10 @@
       <c r="BB16" s="2"/>
       <c r="BC16" s="2"/>
       <c r="BD16" s="2"/>
-      <c r="BE16" s="1"/>
+      <c r="BE16" s="2"/>
+      <c r="BF16" s="1"/>
     </row>
-    <row r="17" spans="1:57" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:58" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
         <v>68</v>
       </c>
@@ -2679,8 +2757,12 @@
       <c r="X17" s="3">
         <v>55</v>
       </c>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
+      <c r="Y17" s="3">
+        <v>30</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0</v>
+      </c>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
@@ -2692,7 +2774,7 @@
       <c r="AI17" s="3"/>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
-      <c r="AL17" s="2"/>
+      <c r="AL17" s="3"/>
       <c r="AM17" s="2"/>
       <c r="AN17" s="2"/>
       <c r="AO17" s="2"/>
@@ -2711,9 +2793,10 @@
       <c r="BB17" s="2"/>
       <c r="BC17" s="2"/>
       <c r="BD17" s="2"/>
-      <c r="BE17" s="1"/>
+      <c r="BE17" s="2"/>
+      <c r="BF17" s="1"/>
     </row>
-    <row r="18" spans="1:57" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:58" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A18" s="5" t="s">
         <v>77</v>
       </c>
@@ -2748,7 +2831,7 @@
         <v>87</v>
       </c>
       <c r="L18" s="3">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M18" s="3">
         <v>94</v>
@@ -2786,8 +2869,12 @@
       <c r="X18" s="3">
         <v>0</v>
       </c>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
+      <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0</v>
+      </c>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
@@ -2799,7 +2886,7 @@
       <c r="AI18" s="3"/>
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
-      <c r="AL18" s="2"/>
+      <c r="AL18" s="3"/>
       <c r="AM18" s="2"/>
       <c r="AN18" s="2"/>
       <c r="AO18" s="2"/>
@@ -2818,9 +2905,10 @@
       <c r="BB18" s="2"/>
       <c r="BC18" s="2"/>
       <c r="BD18" s="2"/>
-      <c r="BE18" s="1"/>
+      <c r="BE18" s="2"/>
+      <c r="BF18" s="1"/>
     </row>
-    <row r="19" spans="1:57" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:58" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
         <v>66</v>
       </c>
@@ -2893,8 +2981,12 @@
       <c r="X19" s="3">
         <v>90</v>
       </c>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
+      <c r="Y19" s="3">
+        <v>8</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>71</v>
+      </c>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
@@ -2906,7 +2998,7 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
-      <c r="AL19" s="2"/>
+      <c r="AL19" s="3"/>
       <c r="AM19" s="2"/>
       <c r="AN19" s="2"/>
       <c r="AO19" s="2"/>
@@ -2925,9 +3017,10 @@
       <c r="BB19" s="2"/>
       <c r="BC19" s="2"/>
       <c r="BD19" s="2"/>
-      <c r="BE19" s="1"/>
+      <c r="BE19" s="2"/>
+      <c r="BF19" s="1"/>
     </row>
-    <row r="20" spans="1:57" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:58" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A20" s="4" t="s">
         <v>69</v>
       </c>
@@ -3000,8 +3093,12 @@
       <c r="X20" s="3">
         <v>75</v>
       </c>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
@@ -3013,7 +3110,7 @@
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
-      <c r="AL20" s="2"/>
+      <c r="AL20" s="3"/>
       <c r="AM20" s="2"/>
       <c r="AN20" s="2"/>
       <c r="AO20" s="2"/>
@@ -3032,9 +3129,10 @@
       <c r="BB20" s="2"/>
       <c r="BC20" s="2"/>
       <c r="BD20" s="2"/>
-      <c r="BE20" s="1"/>
+      <c r="BE20" s="2"/>
+      <c r="BF20" s="1"/>
     </row>
-    <row r="21" spans="1:57" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:58" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>70</v>
       </c>
@@ -3107,8 +3205,12 @@
       <c r="X21" s="3">
         <v>60</v>
       </c>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
+      <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>9</v>
+      </c>
       <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
@@ -3120,7 +3222,7 @@
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
-      <c r="AL21" s="2"/>
+      <c r="AL21" s="3"/>
       <c r="AM21" s="2"/>
       <c r="AN21" s="2"/>
       <c r="AO21" s="2"/>
@@ -3139,9 +3241,10 @@
       <c r="BB21" s="2"/>
       <c r="BC21" s="2"/>
       <c r="BD21" s="2"/>
-      <c r="BE21" s="1"/>
+      <c r="BE21" s="2"/>
+      <c r="BF21" s="1"/>
     </row>
-    <row r="22" spans="1:57" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:58" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A22" s="4" t="s">
         <v>71</v>
       </c>
@@ -3176,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -3214,8 +3317,12 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
@@ -3227,7 +3334,7 @@
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
-      <c r="AL22" s="2"/>
+      <c r="AL22" s="3"/>
       <c r="AM22" s="2"/>
       <c r="AN22" s="2"/>
       <c r="AO22" s="2"/>
@@ -3240,15 +3347,16 @@
       <c r="AV22" s="2"/>
       <c r="AW22" s="2"/>
       <c r="AX22" s="2"/>
-      <c r="AY22" s="11"/>
-      <c r="AZ22" s="2"/>
+      <c r="AY22" s="2"/>
+      <c r="AZ22" s="11"/>
       <c r="BA22" s="2"/>
       <c r="BB22" s="2"/>
       <c r="BC22" s="2"/>
       <c r="BD22" s="2"/>
-      <c r="BE22" s="1"/>
+      <c r="BE22" s="2"/>
+      <c r="BF22" s="1"/>
     </row>
-    <row r="23" spans="1:57" ht="24.75" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:58" ht="24.75" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
         <v>73</v>
       </c>
@@ -3274,7 +3382,7 @@
         <v>90</v>
       </c>
       <c r="I23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23" s="2">
         <v>86</v>
@@ -3321,8 +3429,12 @@
       <c r="X23" s="3">
         <v>0</v>
       </c>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
+      <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0</v>
+      </c>
       <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="3"/>
@@ -3334,7 +3446,7 @@
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
-      <c r="AL23" s="2"/>
+      <c r="AL23" s="3"/>
       <c r="AM23" s="2"/>
       <c r="AN23" s="2"/>
       <c r="AO23" s="2"/>
@@ -3347,18 +3459,19 @@
       <c r="AV23" s="2"/>
       <c r="AW23" s="2"/>
       <c r="AX23" s="2"/>
-      <c r="AY23" s="11"/>
-      <c r="AZ23" s="2"/>
+      <c r="AY23" s="2"/>
+      <c r="AZ23" s="11"/>
       <c r="BA23" s="2"/>
       <c r="BB23" s="2"/>
       <c r="BC23" s="2"/>
       <c r="BD23" s="2"/>
-      <c r="BE23" s="1"/>
+      <c r="BE23" s="2"/>
+      <c r="BF23" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BD1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:BE1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="B1:BD1">
+  <conditionalFormatting sqref="B1:BE1">
     <cfRule type="expression" dxfId="9" priority="18">
       <formula>AVERAGE(B2:B21) &lt; 80</formula>
     </cfRule>
@@ -3372,7 +3485,7 @@
       <formula>AVERAGE(B2:B21) &lt; 90</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:BD23">
+  <conditionalFormatting sqref="B2:BE23">
     <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>

--- a/static/data/quizz.xlsx
+++ b/static/data/quizz.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DERS\Archive\web\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3E4467-C4C7-48C9-9D21-8095CBCCF26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31942809-4205-455E-9610-93523E6A87E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2023-2024" sheetId="2" r:id="rId1"/>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="Z2" s="3">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
@@ -1190,10 +1190,10 @@
         <v>95</v>
       </c>
       <c r="Y3" s="3">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="Z3" s="3">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
@@ -1414,7 +1414,7 @@
         <v>80</v>
       </c>
       <c r="Y5" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Z5" s="3">
         <v>69</v>
@@ -1526,7 +1526,7 @@
         <v>95</v>
       </c>
       <c r="Y6" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Z6" s="3">
         <v>83</v>
@@ -2086,7 +2086,7 @@
         <v>95</v>
       </c>
       <c r="Y11" s="3">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="Z11" s="3">
         <v>80</v>
@@ -2310,7 +2310,7 @@
         <v>80</v>
       </c>
       <c r="Y13" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z13" s="3">
         <v>89</v>
@@ -3094,7 +3094,7 @@
         <v>75</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
